--- a/public/downloads/YohannesCombined2023.xlsx
+++ b/public/downloads/YohannesCombined2023.xlsx
@@ -8,21 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="48">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -54,10 +56,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -133,6 +135,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
@@ -630,10 +653,10 @@
         <v>11277</v>
       </c>
       <c r="N3" s="5">
-        <v>344043.2737772465</v>
+        <v>344043273.7772465</v>
       </c>
       <c r="O3" s="4">
-        <v>0.04945758378013212</v>
+        <v>49.45758378013212</v>
       </c>
       <c r="P3" s="5">
         <v>6956330</v>
@@ -662,7 +685,7 @@
         <v>0.1507493127604859</v>
       </c>
       <c r="H4" s="4">
-        <v>0.8771575634361395</v>
+        <v>0.8771575634361394</v>
       </c>
       <c r="I4" s="4">
         <v>0.5194295818821412</v>
@@ -680,10 +703,10 @@
         <v>11277</v>
       </c>
       <c r="N4" s="5">
-        <v>207766.944644928</v>
+        <v>207766944.644928</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06646185757015688</v>
+        <v>66.46185757015688</v>
       </c>
       <c r="P4" s="5">
         <v>3126108</v>
@@ -730,10 +753,10 @@
         <v>11277</v>
       </c>
       <c r="N5" s="5">
-        <v>289920.3710975647</v>
+        <v>289920371.0975647</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1032586963597597</v>
+        <v>103.2586963597598</v>
       </c>
       <c r="P5" s="5">
         <v>2807709</v>
@@ -780,10 +803,10 @@
         <v>11277</v>
       </c>
       <c r="N6" s="5">
-        <v>229506.4745569229</v>
+        <v>229506474.5569229</v>
       </c>
       <c r="O6" s="4">
-        <v>0.07562398723783943</v>
+        <v>75.62398723783943</v>
       </c>
       <c r="P6" s="5">
         <v>3034837</v>
@@ -830,10 +853,10 @@
         <v>11277</v>
       </c>
       <c r="N7" s="5">
-        <v>402173.4417154789</v>
+        <v>402173441.7154789</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1315887268965812</v>
+        <v>131.5887268965812</v>
       </c>
       <c r="P7" s="5">
         <v>3056291</v>
@@ -880,10 +903,10 @@
         <v>11277</v>
       </c>
       <c r="N8" s="5">
-        <v>109432.6969356537</v>
+        <v>109432696.9356537</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03495414738821486</v>
+        <v>34.95414738821486</v>
       </c>
       <c r="P8" s="5">
         <v>3130750</v>
@@ -930,10 +953,10 @@
         <v>7150</v>
       </c>
       <c r="N9" s="5">
-        <v>85913.80158638954</v>
+        <v>85913801.58638954</v>
       </c>
       <c r="O9" s="4">
-        <v>0.04299243403992877</v>
+        <v>42.99243403992877</v>
       </c>
       <c r="P9" s="5">
         <v>1998347</v>
@@ -959,7 +982,1182 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.401548721384838</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3091621474749738</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4.535425001551237</v>
+      </c>
+      <c r="E3" s="4">
+        <v>65.94783735177823</v>
+      </c>
+      <c r="F3" s="4">
+        <v>61.67995813448263</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3219</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1110</v>
+      </c>
+      <c r="I3" s="5">
+        <v>865</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1244</v>
+      </c>
+      <c r="K3" s="5">
+        <v>78</v>
+      </c>
+      <c r="L3" s="5">
+        <v>993</v>
+      </c>
+      <c r="M3" s="5">
+        <v>173</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7519087523162957</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1283</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.157342656427446</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5478620340672388</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1124</v>
+      </c>
+      <c r="S3" s="5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4903796646907053</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2463281497406096</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3001006707649222</v>
+      </c>
+      <c r="E4" s="4">
+        <v>78.70703781668476</v>
+      </c>
+      <c r="F4" s="4">
+        <v>75.73498891191787</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3209</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2192</v>
+      </c>
+      <c r="I4" s="5">
+        <v>395</v>
+      </c>
+      <c r="J4" s="5">
+        <v>622</v>
+      </c>
+      <c r="K4" s="5">
+        <v>63</v>
+      </c>
+      <c r="L4" s="5">
+        <v>557</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1266095961448367</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2194</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4734854640204902</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2070134551188794</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2192</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.183424858092127</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3352091043300657</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2.266177854891979</v>
+      </c>
+      <c r="E5" s="4">
+        <v>68.37162911284801</v>
+      </c>
+      <c r="F5" s="4">
+        <v>60.76244245944202</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3209</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1155</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1179</v>
+      </c>
+      <c r="J5" s="5">
+        <v>875</v>
+      </c>
+      <c r="K5" s="5">
+        <v>68</v>
+      </c>
+      <c r="L5" s="5">
+        <v>691</v>
+      </c>
+      <c r="M5" s="5">
+        <v>116</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2282644598926001</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1271</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.189601668056575</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5069303205738879</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1192</v>
+      </c>
+      <c r="S5" s="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.588108222348733</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.3980701770018633</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3.197207984373066</v>
+      </c>
+      <c r="E6" s="4">
+        <v>61.79303550688564</v>
+      </c>
+      <c r="F6" s="4">
+        <v>56.16718502755484</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1640</v>
+      </c>
+      <c r="H6" s="5">
+        <v>468</v>
+      </c>
+      <c r="I6" s="5">
+        <v>624</v>
+      </c>
+      <c r="J6" s="5">
+        <v>548</v>
+      </c>
+      <c r="K6" s="5">
+        <v>62</v>
+      </c>
+      <c r="L6" s="5">
+        <v>478</v>
+      </c>
+      <c r="M6" s="5">
+        <v>8</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.148935257924732</v>
+      </c>
+      <c r="O6" s="5">
+        <v>476</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.553829056660188</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.4102564879028834</v>
+      </c>
+      <c r="R6" s="5">
+        <v>468</v>
+      </c>
+      <c r="S6" s="5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.877779465260664</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7042699027145001</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2.061274981562772</v>
+      </c>
+      <c r="E3" s="4">
+        <v>66.35184926076209</v>
+      </c>
+      <c r="F3" s="4">
+        <v>63.95884961666312</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2042</v>
+      </c>
+      <c r="H3" s="5">
+        <v>617</v>
+      </c>
+      <c r="I3" s="5">
+        <v>538</v>
+      </c>
+      <c r="J3" s="5">
+        <v>887</v>
+      </c>
+      <c r="K3" s="5">
+        <v>59</v>
+      </c>
+      <c r="L3" s="5">
+        <v>610</v>
+      </c>
+      <c r="M3" s="5">
+        <v>218</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.229194191965155</v>
+      </c>
+      <c r="O3" s="5">
+        <v>835</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.492965701987074</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8494123584204671</v>
+      </c>
+      <c r="R3" s="5">
+        <v>753</v>
+      </c>
+      <c r="S3" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6407041391878374</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3391166995501639</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3885865454700844</v>
+      </c>
+      <c r="E4" s="4">
+        <v>72.06632235203668</v>
+      </c>
+      <c r="F4" s="4">
+        <v>71.87221938228663</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2035</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1259</v>
+      </c>
+      <c r="I4" s="5">
+        <v>316</v>
+      </c>
+      <c r="J4" s="5">
+        <v>460</v>
+      </c>
+      <c r="K4" s="5">
+        <v>79</v>
+      </c>
+      <c r="L4" s="5">
+        <v>379</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.07976625401243241</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1261</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6456050177757514</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3312311343967115</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1259</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.866922353464315</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4988425237338195</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.836117046425005</v>
+      </c>
+      <c r="E5" s="4">
+        <v>65.96338138429972</v>
+      </c>
+      <c r="F5" s="4">
+        <v>63.31306483256988</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2016</v>
+      </c>
+      <c r="H5" s="5">
+        <v>918</v>
+      </c>
+      <c r="I5" s="5">
+        <v>572</v>
+      </c>
+      <c r="J5" s="5">
+        <v>526</v>
+      </c>
+      <c r="K5" s="5">
+        <v>66</v>
+      </c>
+      <c r="L5" s="5">
+        <v>456</v>
+      </c>
+      <c r="M5" s="5">
+        <v>4</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.4434078665638476</v>
+      </c>
+      <c r="O5" s="5">
+        <v>922</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7836724188751084</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4242267840738337</v>
+      </c>
+      <c r="R5" s="5">
+        <v>922</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.251738241952548</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.6571506517779335</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.232070937016796</v>
+      </c>
+      <c r="E6" s="4">
+        <v>61.41660069893612</v>
+      </c>
+      <c r="F6" s="4">
+        <v>57.74181498013676</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1057</v>
+      </c>
+      <c r="H6" s="5">
+        <v>302</v>
+      </c>
+      <c r="I6" s="5">
+        <v>409</v>
+      </c>
+      <c r="J6" s="5">
+        <v>346</v>
+      </c>
+      <c r="K6" s="5">
+        <v>52</v>
+      </c>
+      <c r="L6" s="5">
+        <v>289</v>
+      </c>
+      <c r="M6" s="5">
+        <v>5</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.1001282567255351</v>
+      </c>
+      <c r="O6" s="5">
+        <v>307</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.258756353673384</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6376493719841283</v>
+      </c>
+      <c r="R6" s="5">
+        <v>300</v>
+      </c>
+      <c r="S6" s="5">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>38.21938458809967</v>
+      </c>
+      <c r="C3" s="3">
+        <v>17.45144985368449</v>
+      </c>
+      <c r="D3" s="3">
+        <v>44.32916555821584</v>
+      </c>
+      <c r="E3" s="3">
+        <v>16.38733705772812</v>
+      </c>
+      <c r="F3" s="3">
+        <v>25.99095504123437</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.950873459253348</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2.027209346528718</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.4686764223596485</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.960316552960142</v>
+      </c>
+      <c r="K3" s="4">
+        <v>67.17308542642027</v>
+      </c>
+      <c r="L3" s="4">
+        <v>62.98681523776191</v>
+      </c>
+      <c r="M3" s="5">
+        <v>11277</v>
+      </c>
+      <c r="N3" s="5">
+        <v>344043273.7772465</v>
+      </c>
+      <c r="O3" s="4">
+        <v>49.45758378013212</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6956330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>61.73627737873548</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15.65132570719163</v>
+      </c>
+      <c r="D4" s="3">
+        <v>22.61239691407289</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5.772811918063315</v>
+      </c>
+      <c r="F4" s="3">
+        <v>16.70657089651503</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.1330140994945464</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.7886458390658142</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3655402516626357</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4493739912221751</v>
+      </c>
+      <c r="K4" s="4">
+        <v>71.8980659568962</v>
+      </c>
+      <c r="L4" s="4">
+        <v>71.65465472971751</v>
+      </c>
+      <c r="M4" s="5">
+        <v>11277</v>
+      </c>
+      <c r="N4" s="5">
+        <v>207766944.644928</v>
+      </c>
+      <c r="O4" s="4">
+        <v>66.46185757015688</v>
+      </c>
+      <c r="P4" s="5">
+        <v>3126108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>62.02890839762348</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16.39620466436109</v>
+      </c>
+      <c r="D5" s="3">
+        <v>21.57488693801543</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4.886051254766339</v>
+      </c>
+      <c r="F5" s="3">
+        <v>15.96169193934557</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.7271437439035204</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.8419034142741533</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3599688022148837</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.35763420402078</v>
+      </c>
+      <c r="K5" s="4">
+        <v>74.04695850141067</v>
+      </c>
+      <c r="L5" s="4">
+        <v>72.50507308435401</v>
+      </c>
+      <c r="M5" s="5">
+        <v>11277</v>
+      </c>
+      <c r="N5" s="5">
+        <v>289920371.0975647</v>
+      </c>
+      <c r="O5" s="4">
+        <v>103.2586963597598</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2807709</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>53.18790458455263</v>
+      </c>
+      <c r="C6" s="3">
+        <v>21.31772634565931</v>
+      </c>
+      <c r="D6" s="3">
+        <v>25.49436906978806</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.431763766959298</v>
+      </c>
+      <c r="F6" s="3">
+        <v>21.76110667730779</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.3014986255209718</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.7029629419240737</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3137813304650144</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.6988343992379465</v>
+      </c>
+      <c r="K6" s="4">
+        <v>72.07990618434128</v>
+      </c>
+      <c r="L6" s="4">
+        <v>68.48542072230721</v>
+      </c>
+      <c r="M6" s="5">
+        <v>11277</v>
+      </c>
+      <c r="N6" s="5">
+        <v>229506474.5569229</v>
+      </c>
+      <c r="O6" s="4">
+        <v>75.62398723783943</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3034837</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>56.34477254588987</v>
+      </c>
+      <c r="C7" s="3">
+        <v>18.51556264964086</v>
+      </c>
+      <c r="D7" s="3">
+        <v>25.13966480446928</v>
+      </c>
+      <c r="E7" s="3">
+        <v>7.156158552806597</v>
+      </c>
+      <c r="F7" s="3">
+        <v>14.11722975968786</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.866276491974816</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.22606338486996</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.4624764982759597</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.101451322939463</v>
+      </c>
+      <c r="K7" s="4">
+        <v>79.51246863913607</v>
+      </c>
+      <c r="L7" s="4">
+        <v>75.60025860876985</v>
+      </c>
+      <c r="M7" s="5">
+        <v>11277</v>
+      </c>
+      <c r="N7" s="5">
+        <v>402173441.7154789</v>
+      </c>
+      <c r="O7" s="4">
+        <v>131.5887268965812</v>
+      </c>
+      <c r="P7" s="5">
+        <v>3056291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>44.12521060565754</v>
+      </c>
+      <c r="C8" s="3">
+        <v>27.16147911678638</v>
+      </c>
+      <c r="D8" s="3">
+        <v>28.71331027755609</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.403121397534806</v>
+      </c>
+      <c r="F8" s="3">
+        <v>24.11102243504478</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2.199166444976501</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.315031681368978</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3749661170367331</v>
+      </c>
+      <c r="J8" s="4">
+        <v>2.371242441394443</v>
+      </c>
+      <c r="K8" s="4">
+        <v>69.66410471255988</v>
+      </c>
+      <c r="L8" s="4">
+        <v>64.61667340168334</v>
+      </c>
+      <c r="M8" s="5">
+        <v>11277</v>
+      </c>
+      <c r="N8" s="5">
+        <v>109432696.9356537</v>
+      </c>
+      <c r="O8" s="4">
+        <v>34.95414738821486</v>
+      </c>
+      <c r="P8" s="5">
+        <v>3130750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45.23076923076923</v>
+      </c>
+      <c r="C9" s="3">
+        <v>25.66433566433566</v>
+      </c>
+      <c r="D9" s="3">
+        <v>29.10489510489511</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.58041958041958</v>
+      </c>
+      <c r="F9" s="3">
+        <v>24.25174825174825</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.0171791939743</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.5068210917153323</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.9170513713290047</v>
+      </c>
+      <c r="K9" s="4">
+        <v>67.13915608201316</v>
+      </c>
+      <c r="L9" s="4">
+        <v>65.10995447505513</v>
+      </c>
+      <c r="M9" s="5">
+        <v>7150</v>
+      </c>
+      <c r="N9" s="5">
+        <v>85913801.58638954</v>
+      </c>
+      <c r="O9" s="4">
+        <v>42.99243403992877</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1998347</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1073,16 +2271,16 @@
         <v>142</v>
       </c>
       <c r="K3" s="5">
-        <v>1545</v>
+        <v>340</v>
       </c>
       <c r="L3" s="5">
-        <v>3325</v>
+        <v>2144</v>
       </c>
       <c r="M3" s="5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="N3" s="5">
-        <v>1782</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -1117,16 +2315,16 @@
         <v>223</v>
       </c>
       <c r="K4" s="5">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="L4" s="5">
-        <v>1866</v>
+        <v>1453</v>
       </c>
       <c r="M4" s="5">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>1122</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -1161,16 +2359,16 @@
         <v>22</v>
       </c>
       <c r="K5" s="5">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="L5" s="5">
-        <v>1835</v>
+        <v>1475</v>
       </c>
       <c r="M5" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N5" s="5">
-        <v>615</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -1205,16 +2403,16 @@
         <v>120</v>
       </c>
       <c r="K6" s="5">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="L6" s="5">
-        <v>2333</v>
+        <v>2116</v>
       </c>
       <c r="M6" s="5">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="N6" s="5">
-        <v>1044</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -1249,16 +2447,16 @@
         <v>88</v>
       </c>
       <c r="K7" s="5">
-        <v>214</v>
+        <v>31</v>
       </c>
       <c r="L7" s="5">
-        <v>1774</v>
+        <v>1323</v>
       </c>
       <c r="M7" s="5">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="N7" s="5">
-        <v>603</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -1293,16 +2491,16 @@
         <v>57</v>
       </c>
       <c r="K8" s="5">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="L8" s="5">
-        <v>2464</v>
+        <v>2315</v>
       </c>
       <c r="M8" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>1097</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -1337,16 +2535,16 @@
         <v>64</v>
       </c>
       <c r="K9" s="5">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="L9" s="5">
-        <v>1599</v>
+        <v>1419</v>
       </c>
       <c r="M9" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>885</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -1362,9 +2560,412 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4310</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1968</v>
+      </c>
+      <c r="D3" s="5">
+        <v>4999</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1848</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2931</v>
+      </c>
+      <c r="G3" s="5">
+        <v>220</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1847</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1744</v>
+      </c>
+      <c r="J3" s="5">
+        <v>142</v>
+      </c>
+      <c r="K3" s="5">
+        <v>340</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2144</v>
+      </c>
+      <c r="M3" s="5">
+        <v>6</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>6962</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1765</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2550</v>
+      </c>
+      <c r="E4" s="5">
+        <v>651</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1884</v>
+      </c>
+      <c r="G4" s="5">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
+        <v>650</v>
+      </c>
+      <c r="I4" s="5">
+        <v>466</v>
+      </c>
+      <c r="J4" s="5">
+        <v>223</v>
+      </c>
+      <c r="K4" s="5">
+        <v>18</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1453</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6995</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1849</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2433</v>
+      </c>
+      <c r="E5" s="5">
+        <v>551</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1800</v>
+      </c>
+      <c r="G5" s="5">
+        <v>82</v>
+      </c>
+      <c r="H5" s="5">
+        <v>551</v>
+      </c>
+      <c r="I5" s="5">
+        <v>529</v>
+      </c>
+      <c r="J5" s="5">
+        <v>22</v>
+      </c>
+      <c r="K5" s="5">
+        <v>48</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1475</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2</v>
+      </c>
+      <c r="N5" s="5">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>5998</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2404</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2875</v>
+      </c>
+      <c r="E6" s="5">
+        <v>387</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2454</v>
+      </c>
+      <c r="G6" s="5">
+        <v>34</v>
+      </c>
+      <c r="H6" s="5">
+        <v>386</v>
+      </c>
+      <c r="I6" s="5">
+        <v>280</v>
+      </c>
+      <c r="J6" s="5">
+        <v>120</v>
+      </c>
+      <c r="K6" s="5">
+        <v>27</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2116</v>
+      </c>
+      <c r="M6" s="5">
+        <v>33</v>
+      </c>
+      <c r="N6" s="5">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6354</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2088</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2835</v>
+      </c>
+      <c r="E7" s="5">
+        <v>807</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1592</v>
+      </c>
+      <c r="G7" s="5">
+        <v>436</v>
+      </c>
+      <c r="H7" s="5">
+        <v>807</v>
+      </c>
+      <c r="I7" s="5">
+        <v>721</v>
+      </c>
+      <c r="J7" s="5">
+        <v>88</v>
+      </c>
+      <c r="K7" s="5">
+        <v>31</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1323</v>
+      </c>
+      <c r="M7" s="5">
+        <v>9</v>
+      </c>
+      <c r="N7" s="5">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4976</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3063</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3238</v>
+      </c>
+      <c r="E8" s="5">
+        <v>271</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2719</v>
+      </c>
+      <c r="G8" s="5">
+        <v>248</v>
+      </c>
+      <c r="H8" s="5">
+        <v>271</v>
+      </c>
+      <c r="I8" s="5">
+        <v>214</v>
+      </c>
+      <c r="J8" s="5">
+        <v>57</v>
+      </c>
+      <c r="K8" s="5">
+        <v>65</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2315</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3234</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1835</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2081</v>
+      </c>
+      <c r="E9" s="5">
+        <v>256</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1734</v>
+      </c>
+      <c r="G9" s="5">
+        <v>91</v>
+      </c>
+      <c r="H9" s="5">
+        <v>255</v>
+      </c>
+      <c r="I9" s="5">
+        <v>208</v>
+      </c>
+      <c r="J9" s="5">
+        <v>64</v>
+      </c>
+      <c r="K9" s="5">
+        <v>23</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1419</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>789</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1375,9 +2976,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -1411,8 +3018,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1434,10 +3049,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4">
         <v>4.246949254434953</v>
@@ -1475,10 +3108,28 @@
       <c r="M3" s="5">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.596768151796113</v>
+      </c>
+      <c r="O3" s="5">
+        <v>967</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.887046901431867</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.199706253120331</v>
+      </c>
+      <c r="R3" s="5">
+        <v>838</v>
+      </c>
+      <c r="S3" s="5">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>0.5936842695871267</v>
@@ -1516,10 +3167,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.03379733755591832</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2056</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.594993188740592</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2197183344398961</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2054</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4">
         <v>1.644141676346117</v>
@@ -1557,10 +3226,28 @@
       <c r="M5" s="5">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.03020771800183475</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1053</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.642319335572921</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3756032259613731</v>
+      </c>
+      <c r="R5" s="5">
+        <v>988</v>
+      </c>
+      <c r="S5" s="5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4">
         <v>1.932063841155006</v>
@@ -1598,9 +3285,27 @@
       <c r="M6" s="5">
         <v>24</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.218054548463412</v>
+      </c>
+      <c r="O6" s="5">
+        <v>454</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.93225605766653</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.4470792885252649</v>
+      </c>
+      <c r="R6" s="5">
+        <v>430</v>
+      </c>
+      <c r="S6" s="5">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1611,14 +3316,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1629,9 +3335,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -1665,8 +3377,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1688,10 +3408,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4">
         <v>1.107351838108744</v>
@@ -1729,10 +3467,28 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.830482251149127</v>
+      </c>
+      <c r="O3" s="5">
+        <v>2104</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8056455939635468</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4055721222096743</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2102</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>0.6835244849243992</v>
@@ -1770,10 +3526,28 @@
       <c r="M4" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1264583988262083</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2257</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6742163450162356</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3061198349553497</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2254</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4">
         <v>0.7089411600118909</v>
@@ -1811,10 +3585,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.06304326776036372</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1824</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7085594795007903</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3128221560639828</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1824</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4">
         <v>1.133364647193136</v>
@@ -1852,9 +3644,27 @@
       <c r="M6" s="5">
         <v>10</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.01486321793101811</v>
+      </c>
+      <c r="O6" s="5">
+        <v>792</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.135889231281337</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5521699623279682</v>
+      </c>
+      <c r="R6" s="5">
+        <v>782</v>
+      </c>
+      <c r="S6" s="5">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1865,14 +3675,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1883,9 +3694,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -1919,8 +3736,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1942,10 +3767,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4">
         <v>1.327178561834792</v>
@@ -1983,10 +3826,28 @@
       <c r="M3" s="5">
         <v>120</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5654984684956192</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1919</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.2838818691662</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5821786606092798</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1869</v>
+      </c>
+      <c r="S3" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>0.4302432614511209</v>
@@ -2024,10 +3885,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.01504386947535139</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2392</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4308589635550376</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1835396179086448</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2390</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4">
         <v>0.7240419270766534</v>
@@ -2065,10 +3944,28 @@
       <c r="M5" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.3337701042036493</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1855</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7098370127448501</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3534850126525417</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1846</v>
+      </c>
+      <c r="S5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4">
         <v>1.059112736333294</v>
@@ -2106,9 +4003,27 @@
       <c r="M6" s="5">
         <v>26</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.4174573775069132</v>
+      </c>
+      <c r="O6" s="5">
+        <v>911</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.037094925595909</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3805582411866453</v>
+      </c>
+      <c r="R6" s="5">
+        <v>890</v>
+      </c>
+      <c r="S6" s="5">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2119,14 +4034,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2137,9 +4053,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -2173,8 +4095,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2196,10 +4126,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4">
         <v>1.005464654820073</v>
@@ -2237,10 +4185,28 @@
       <c r="M3" s="5">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5660101474158261</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1692</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8494927251575743</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3889609092000186</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1669</v>
+      </c>
+      <c r="S3" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>0.5686031569406986</v>
@@ -2278,10 +4244,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.085681912473803</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2074</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5611429877440305</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2470467522662632</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2072</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4">
         <v>0.6009414815514348</v>
@@ -2319,10 +4303,28 @@
       <c r="M5" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.2796177613218486</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1620</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5700554384683532</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2773800447849948</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1616</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4">
         <v>0.9685007443538896</v>
@@ -2360,9 +4362,27 @@
       <c r="M6" s="5">
         <v>3</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.2747258130716398</v>
+      </c>
+      <c r="O6" s="5">
+        <v>646</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9529147951707374</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.4255189385430211</v>
+      </c>
+      <c r="R6" s="5">
+        <v>641</v>
+      </c>
+      <c r="S6" s="5">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2373,14 +4393,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2391,9 +4412,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -2427,8 +4454,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2450,10 +4485,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4">
         <v>2.664094445796731</v>
@@ -2491,10 +4544,28 @@
       <c r="M3" s="5">
         <v>364</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.548832496730614</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1655</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.606364794722914</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.357793604604853</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1304</v>
+      </c>
+      <c r="S3" s="5">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4">
         <v>0.3413611511796414</v>
@@ -2532,10 +4603,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.063568789581591</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2494</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3336822220509059</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1226570495408442</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2492</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4">
         <v>0.772847521905723</v>
@@ -2573,10 +4662,28 @@
       <c r="M5" s="5">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.508411590945261</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1854</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7162632061808079</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3231448111937371</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1822</v>
+      </c>
+      <c r="S5" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4">
         <v>1.323200958148771</v>
@@ -2614,9 +4721,27 @@
       <c r="M6" s="5">
         <v>54</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.6633585853704907</v>
+      </c>
+      <c r="O6" s="5">
+        <v>787</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.260459535225558</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3717141252580798</v>
+      </c>
+      <c r="R6" s="5">
+        <v>736</v>
+      </c>
+      <c r="S6" s="5">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2627,514 +4752,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2.401548721384838</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3091621474749738</v>
-      </c>
-      <c r="D3" s="4">
-        <v>4.535425001551237</v>
-      </c>
-      <c r="E3" s="4">
-        <v>65.94783735177823</v>
-      </c>
-      <c r="F3" s="4">
-        <v>61.67995813448263</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3219</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1110</v>
-      </c>
-      <c r="I3" s="5">
-        <v>865</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1244</v>
-      </c>
-      <c r="K3" s="5">
-        <v>78</v>
-      </c>
-      <c r="L3" s="5">
-        <v>993</v>
-      </c>
-      <c r="M3" s="5">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4903796646907053</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2463281497406096</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3001006707649222</v>
-      </c>
-      <c r="E4" s="4">
-        <v>78.70703781668476</v>
-      </c>
-      <c r="F4" s="4">
-        <v>75.73498891191787</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3209</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2192</v>
-      </c>
-      <c r="I4" s="5">
-        <v>395</v>
-      </c>
-      <c r="J4" s="5">
-        <v>622</v>
-      </c>
-      <c r="K4" s="5">
-        <v>63</v>
-      </c>
-      <c r="L4" s="5">
-        <v>557</v>
-      </c>
-      <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.183424858092127</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3352091043300657</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2.266177854891979</v>
-      </c>
-      <c r="E5" s="4">
-        <v>68.37162911284801</v>
-      </c>
-      <c r="F5" s="4">
-        <v>60.76244245944202</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3209</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1155</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1179</v>
-      </c>
-      <c r="J5" s="5">
-        <v>875</v>
-      </c>
-      <c r="K5" s="5">
-        <v>68</v>
-      </c>
-      <c r="L5" s="5">
-        <v>691</v>
-      </c>
-      <c r="M5" s="5">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.588108222348733</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3980701770018633</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3.197207984373066</v>
-      </c>
-      <c r="E6" s="4">
-        <v>61.79303550688564</v>
-      </c>
-      <c r="F6" s="4">
-        <v>56.16718502755484</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1640</v>
-      </c>
-      <c r="H6" s="5">
-        <v>468</v>
-      </c>
-      <c r="I6" s="5">
-        <v>624</v>
-      </c>
-      <c r="J6" s="5">
-        <v>548</v>
-      </c>
-      <c r="K6" s="5">
-        <v>62</v>
-      </c>
-      <c r="L6" s="5">
-        <v>478</v>
-      </c>
-      <c r="M6" s="5">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.877779465260664</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7042699027145001</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2.061274981562772</v>
-      </c>
-      <c r="E3" s="4">
-        <v>66.35184926076209</v>
-      </c>
-      <c r="F3" s="4">
-        <v>63.95884961666312</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2042</v>
-      </c>
-      <c r="H3" s="5">
-        <v>617</v>
-      </c>
-      <c r="I3" s="5">
-        <v>538</v>
-      </c>
-      <c r="J3" s="5">
-        <v>887</v>
-      </c>
-      <c r="K3" s="5">
-        <v>59</v>
-      </c>
-      <c r="L3" s="5">
-        <v>610</v>
-      </c>
-      <c r="M3" s="5">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6407041391878374</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3391166995501639</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3885865454700844</v>
-      </c>
-      <c r="E4" s="4">
-        <v>72.06632235203668</v>
-      </c>
-      <c r="F4" s="4">
-        <v>71.87221938228663</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2035</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1259</v>
-      </c>
-      <c r="I4" s="5">
-        <v>316</v>
-      </c>
-      <c r="J4" s="5">
-        <v>460</v>
-      </c>
-      <c r="K4" s="5">
-        <v>79</v>
-      </c>
-      <c r="L4" s="5">
-        <v>379</v>
-      </c>
-      <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.866922353464315</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4988425237338195</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.836117046425005</v>
-      </c>
-      <c r="E5" s="4">
-        <v>65.96338138429972</v>
-      </c>
-      <c r="F5" s="4">
-        <v>63.31306483256988</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2016</v>
-      </c>
-      <c r="H5" s="5">
-        <v>918</v>
-      </c>
-      <c r="I5" s="5">
-        <v>572</v>
-      </c>
-      <c r="J5" s="5">
-        <v>526</v>
-      </c>
-      <c r="K5" s="5">
-        <v>66</v>
-      </c>
-      <c r="L5" s="5">
-        <v>456</v>
-      </c>
-      <c r="M5" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.251738241952548</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.6571506517779335</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1.232070937016796</v>
-      </c>
-      <c r="E6" s="4">
-        <v>61.41660069893612</v>
-      </c>
-      <c r="F6" s="4">
-        <v>57.74181498013676</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1057</v>
-      </c>
-      <c r="H6" s="5">
-        <v>302</v>
-      </c>
-      <c r="I6" s="5">
-        <v>409</v>
-      </c>
-      <c r="J6" s="5">
-        <v>346</v>
-      </c>
-      <c r="K6" s="5">
-        <v>52</v>
-      </c>
-      <c r="L6" s="5">
-        <v>289</v>
-      </c>
-      <c r="M6" s="5">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/YohannesCombined2023.xlsx
+++ b/public/downloads/YohannesCombined2023.xlsx
@@ -1128,22 +1128,22 @@
         <v>173</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7519087523162957</v>
+        <v>0.2825533157694782</v>
       </c>
       <c r="O3" s="5">
         <v>1283</v>
       </c>
       <c r="P3" s="4">
-        <v>2.157342656427446</v>
+        <v>2.250051638276363</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5478620340672388</v>
+        <v>0.2606534098388495</v>
       </c>
       <c r="R3" s="5">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="S3" s="5">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1187,16 +1187,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1266095961448367</v>
+        <v>0.1538205779156794</v>
       </c>
       <c r="O4" s="5">
         <v>2194</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4734854640204902</v>
+        <v>0.4756962559359346</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2070134551188794</v>
+        <v>0.205712835769413</v>
       </c>
       <c r="R4" s="5">
         <v>2192</v>
@@ -1246,22 +1246,22 @@
         <v>116</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2282644598926001</v>
+        <v>-0.05059647475348683</v>
       </c>
       <c r="O5" s="5">
         <v>1271</v>
       </c>
       <c r="P5" s="4">
-        <v>1.189601668056575</v>
+        <v>1.194198024647616</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5069303205738879</v>
+        <v>0.3208759295394438</v>
       </c>
       <c r="R5" s="5">
-        <v>1192</v>
+        <v>1152</v>
       </c>
       <c r="S5" s="5">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -1305,16 +1305,16 @@
         <v>8</v>
       </c>
       <c r="N6" s="4">
-        <v>0.148935257924732</v>
+        <v>0.03410287807959556</v>
       </c>
       <c r="O6" s="5">
         <v>476</v>
       </c>
       <c r="P6" s="4">
-        <v>1.553829056660188</v>
+        <v>1.578731208446999</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4102564879028834</v>
+        <v>0.3977945443537283</v>
       </c>
       <c r="R6" s="5">
         <v>468</v>
@@ -1487,22 +1487,22 @@
         <v>218</v>
       </c>
       <c r="N3" s="4">
-        <v>1.229194191965155</v>
+        <v>0.8657324673828271</v>
       </c>
       <c r="O3" s="5">
         <v>835</v>
       </c>
       <c r="P3" s="4">
-        <v>1.492965701987074</v>
+        <v>1.513021102924522</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8494123584204671</v>
+        <v>0.6818367516102912</v>
       </c>
       <c r="R3" s="5">
-        <v>753</v>
+        <v>725</v>
       </c>
       <c r="S3" s="5">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1546,16 +1546,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.07976625401243241</v>
+        <v>0.08093158158209235</v>
       </c>
       <c r="O4" s="5">
         <v>1261</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6456050177757514</v>
+        <v>0.6457549246983922</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3312311343967115</v>
+        <v>0.331219824494795</v>
       </c>
       <c r="R4" s="5">
         <v>1259</v>
@@ -1605,22 +1605,22 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4434078665638476</v>
+        <v>0.2857518060839936</v>
       </c>
       <c r="O5" s="5">
         <v>922</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7836724188751084</v>
+        <v>0.7853021945904649</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4242267840738337</v>
+        <v>0.4034745875848488</v>
       </c>
       <c r="R5" s="5">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -1664,16 +1664,16 @@
         <v>5</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1001282567255351</v>
+        <v>-0.1397440627246169</v>
       </c>
       <c r="O6" s="5">
         <v>307</v>
       </c>
       <c r="P6" s="4">
-        <v>1.258756353673384</v>
+        <v>1.263365625369935</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6376493719841283</v>
+        <v>0.6360348704294316</v>
       </c>
       <c r="R6" s="5">
         <v>300</v>
@@ -1792,13 +1792,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>38.21938458809967</v>
+        <v>38.27259022789749</v>
       </c>
       <c r="C3" s="3">
         <v>17.45144985368449</v>
       </c>
       <c r="D3" s="3">
-        <v>44.32916555821584</v>
+        <v>44.27595991841802</v>
       </c>
       <c r="E3" s="3">
         <v>16.38733705772812</v>
@@ -1807,16 +1807,16 @@
         <v>25.99095504123437</v>
       </c>
       <c r="G3" s="3">
-        <v>1.950873459253348</v>
+        <v>1.897667819455529</v>
       </c>
       <c r="H3" s="4">
-        <v>2.027209346528718</v>
+        <v>2.061146426195838</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4686764223596485</v>
+        <v>0.2470220862086306</v>
       </c>
       <c r="J3" s="4">
-        <v>3.960316552960142</v>
+        <v>4.02610869824196</v>
       </c>
       <c r="K3" s="4">
         <v>67.17308542642027</v>
@@ -1860,13 +1860,13 @@
         <v>0.1330140994945464</v>
       </c>
       <c r="H4" s="4">
-        <v>0.7886458390658142</v>
+        <v>0.7883705744866745</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3655402516626357</v>
+        <v>0.3635065047350357</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4493739912221751</v>
+        <v>0.4507289943816452</v>
       </c>
       <c r="K4" s="4">
         <v>71.8980659568962</v>
@@ -1892,13 +1892,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>62.02890839762348</v>
+        <v>61.63873370577281</v>
       </c>
       <c r="C5" s="3">
         <v>16.39620466436109</v>
       </c>
       <c r="D5" s="3">
-        <v>21.57488693801543</v>
+        <v>21.9650616298661</v>
       </c>
       <c r="E5" s="3">
         <v>4.886051254766339</v>
@@ -1907,16 +1907,16 @@
         <v>15.96169193934557</v>
       </c>
       <c r="G5" s="3">
-        <v>0.7271437439035204</v>
+        <v>1.11731843575419</v>
       </c>
       <c r="H5" s="4">
-        <v>0.8419034142741533</v>
+        <v>0.8321104455659983</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3599688022148837</v>
+        <v>0.3194046743652851</v>
       </c>
       <c r="J5" s="4">
-        <v>1.35763420402078</v>
+        <v>1.368620193517578</v>
       </c>
       <c r="K5" s="4">
         <v>74.04695850141067</v>
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>53.18790458455263</v>
+        <v>53.16130176465372</v>
       </c>
       <c r="C6" s="3">
         <v>21.31772634565931</v>
       </c>
       <c r="D6" s="3">
-        <v>25.49436906978806</v>
+        <v>25.52097188968697</v>
       </c>
       <c r="E6" s="3">
         <v>3.431763766959298</v>
@@ -1957,16 +1957,16 @@
         <v>21.76110667730779</v>
       </c>
       <c r="G6" s="3">
-        <v>0.3014986255209718</v>
+        <v>0.3281014454198812</v>
       </c>
       <c r="H6" s="4">
-        <v>0.7029629419240737</v>
+        <v>0.7026182495662989</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3137813304650144</v>
+        <v>0.3103927153699828</v>
       </c>
       <c r="J6" s="4">
-        <v>0.6988343992379465</v>
+        <v>0.7010425040254706</v>
       </c>
       <c r="K6" s="4">
         <v>72.07990618434128</v>
@@ -1992,13 +1992,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>56.34477254588987</v>
+        <v>56.21175844639532</v>
       </c>
       <c r="C7" s="3">
         <v>18.51556264964086</v>
       </c>
       <c r="D7" s="3">
-        <v>25.13966480446928</v>
+        <v>25.27267890396382</v>
       </c>
       <c r="E7" s="3">
         <v>7.156158552806597</v>
@@ -2007,16 +2007,16 @@
         <v>14.11722975968786</v>
       </c>
       <c r="G7" s="3">
-        <v>3.866276491974816</v>
+        <v>3.999290591469362</v>
       </c>
       <c r="H7" s="4">
-        <v>1.22606338486996</v>
+        <v>1.190846045572286</v>
       </c>
       <c r="I7" s="4">
-        <v>0.4624764982759597</v>
+        <v>0.1839586867076567</v>
       </c>
       <c r="J7" s="4">
-        <v>2.101451322939463</v>
+        <v>2.082642885335454</v>
       </c>
       <c r="K7" s="4">
         <v>79.51246863913607</v>
@@ -2042,13 +2042,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>44.12521060565754</v>
+        <v>43.70843309390796</v>
       </c>
       <c r="C8" s="3">
         <v>27.16147911678638</v>
       </c>
       <c r="D8" s="3">
-        <v>28.71331027755609</v>
+        <v>29.13008778930567</v>
       </c>
       <c r="E8" s="3">
         <v>2.403121397534806</v>
@@ -2057,16 +2057,16 @@
         <v>24.11102243504478</v>
       </c>
       <c r="G8" s="3">
-        <v>2.199166444976501</v>
+        <v>2.61594395672608</v>
       </c>
       <c r="H8" s="4">
-        <v>1.315031681368978</v>
+        <v>1.347053839838371</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3749661170367331</v>
+        <v>0.2633169633563669</v>
       </c>
       <c r="J8" s="4">
-        <v>2.371242441394443</v>
+        <v>2.43042635370921</v>
       </c>
       <c r="K8" s="4">
         <v>69.66410471255988</v>
@@ -2092,13 +2092,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>45.23076923076923</v>
+        <v>44.78321678321679</v>
       </c>
       <c r="C9" s="3">
         <v>25.66433566433566</v>
       </c>
       <c r="D9" s="3">
-        <v>29.10489510489511</v>
+        <v>29.55244755244755</v>
       </c>
       <c r="E9" s="3">
         <v>3.58041958041958</v>
@@ -2107,16 +2107,16 @@
         <v>24.25174825174825</v>
       </c>
       <c r="G9" s="3">
-        <v>1.272727272727273</v>
+        <v>1.72027972027972</v>
       </c>
       <c r="H9" s="4">
-        <v>1.0171791939743</v>
+        <v>1.024090497096993</v>
       </c>
       <c r="I9" s="4">
-        <v>0.5068210917153323</v>
+        <v>0.4598805548057867</v>
       </c>
       <c r="J9" s="4">
-        <v>0.9170513713290047</v>
+        <v>0.9434768210059992</v>
       </c>
       <c r="K9" s="4">
         <v>67.13915608201316</v>
@@ -2647,13 +2647,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>4310</v>
+        <v>4316</v>
       </c>
       <c r="C3" s="5">
         <v>1968</v>
       </c>
       <c r="D3" s="5">
-        <v>4999</v>
+        <v>4993</v>
       </c>
       <c r="E3" s="5">
         <v>1848</v>
@@ -2662,7 +2662,7 @@
         <v>2931</v>
       </c>
       <c r="G3" s="5">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H3" s="5">
         <v>1847</v>
@@ -2735,13 +2735,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>6995</v>
+        <v>6951</v>
       </c>
       <c r="C5" s="5">
         <v>1849</v>
       </c>
       <c r="D5" s="5">
-        <v>2433</v>
+        <v>2477</v>
       </c>
       <c r="E5" s="5">
         <v>551</v>
@@ -2750,7 +2750,7 @@
         <v>1800</v>
       </c>
       <c r="G5" s="5">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="H5" s="5">
         <v>551</v>
@@ -2779,13 +2779,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>5998</v>
+        <v>5995</v>
       </c>
       <c r="C6" s="5">
         <v>2404</v>
       </c>
       <c r="D6" s="5">
-        <v>2875</v>
+        <v>2878</v>
       </c>
       <c r="E6" s="5">
         <v>387</v>
@@ -2794,7 +2794,7 @@
         <v>2454</v>
       </c>
       <c r="G6" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5">
         <v>386</v>
@@ -2823,13 +2823,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>6354</v>
+        <v>6339</v>
       </c>
       <c r="C7" s="5">
         <v>2088</v>
       </c>
       <c r="D7" s="5">
-        <v>2835</v>
+        <v>2850</v>
       </c>
       <c r="E7" s="5">
         <v>807</v>
@@ -2838,7 +2838,7 @@
         <v>1592</v>
       </c>
       <c r="G7" s="5">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="H7" s="5">
         <v>807</v>
@@ -2867,13 +2867,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>4976</v>
+        <v>4929</v>
       </c>
       <c r="C8" s="5">
         <v>3063</v>
       </c>
       <c r="D8" s="5">
-        <v>3238</v>
+        <v>3285</v>
       </c>
       <c r="E8" s="5">
         <v>271</v>
@@ -2882,7 +2882,7 @@
         <v>2719</v>
       </c>
       <c r="G8" s="5">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="H8" s="5">
         <v>271</v>
@@ -2911,13 +2911,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>3234</v>
+        <v>3202</v>
       </c>
       <c r="C9" s="5">
         <v>1835</v>
       </c>
       <c r="D9" s="5">
-        <v>2081</v>
+        <v>2113</v>
       </c>
       <c r="E9" s="5">
         <v>256</v>
@@ -2926,7 +2926,7 @@
         <v>1734</v>
       </c>
       <c r="G9" s="5">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H9" s="5">
         <v>255</v>
@@ -3109,22 +3109,22 @@
         <v>123</v>
       </c>
       <c r="N3" s="4">
-        <v>1.596768151796113</v>
+        <v>0.4621906776281435</v>
       </c>
       <c r="O3" s="5">
         <v>967</v>
       </c>
       <c r="P3" s="4">
-        <v>3.887046901431867</v>
+        <v>3.971500242611851</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.199706253120331</v>
+        <v>0.2308853393247343</v>
       </c>
       <c r="R3" s="5">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="S3" s="5">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3168,16 +3168,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.03379733755591832</v>
+        <v>0.0418135695740034</v>
       </c>
       <c r="O4" s="5">
         <v>2056</v>
       </c>
       <c r="P4" s="4">
-        <v>0.594993188740592</v>
+        <v>0.5957416106561528</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2197183344398961</v>
+        <v>0.2195649683508559</v>
       </c>
       <c r="R4" s="5">
         <v>2054</v>
@@ -3227,16 +3227,16 @@
         <v>65</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03020771800183475</v>
+        <v>-0.3488000757787972</v>
       </c>
       <c r="O5" s="5">
         <v>1053</v>
       </c>
       <c r="P5" s="4">
-        <v>1.642319335572921</v>
+        <v>1.663946132430728</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3756032259613731</v>
+        <v>0.243773715591952</v>
       </c>
       <c r="R5" s="5">
         <v>988</v>
@@ -3286,16 +3286,16 @@
         <v>24</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.218054548463412</v>
+        <v>-0.3768045391345254</v>
       </c>
       <c r="O6" s="5">
         <v>454</v>
       </c>
       <c r="P6" s="4">
-        <v>1.93225605766653</v>
+        <v>1.956067682729947</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4470792885252649</v>
+        <v>0.4173144690438779</v>
       </c>
       <c r="R6" s="5">
         <v>430</v>
@@ -3468,16 +3468,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.830482251149127</v>
+        <v>0.8490231396851016</v>
       </c>
       <c r="O3" s="5">
         <v>2104</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8056455939635468</v>
+        <v>0.8077088992517033</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4055721222096743</v>
+        <v>0.4053960965563397</v>
       </c>
       <c r="R3" s="5">
         <v>2102</v>
@@ -3527,16 +3527,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1264583988262083</v>
+        <v>0.1822413776562826</v>
       </c>
       <c r="O4" s="5">
         <v>2257</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6742163450162356</v>
+        <v>0.6779857730043526</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3061198349553497</v>
+        <v>0.3028289863074741</v>
       </c>
       <c r="R4" s="5">
         <v>2254</v>
@@ -3586,16 +3586,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.06304326776036372</v>
+        <v>0.07558584823243564</v>
       </c>
       <c r="O5" s="5">
         <v>1824</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7085594795007903</v>
+        <v>0.7094034887147677</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3128221560639828</v>
+        <v>0.3125013669249975</v>
       </c>
       <c r="R5" s="5">
         <v>1824</v>
@@ -3645,16 +3645,16 @@
         <v>10</v>
       </c>
       <c r="N6" s="4">
-        <v>0.01486321793101811</v>
+        <v>-0.09322297793949019</v>
       </c>
       <c r="O6" s="5">
         <v>792</v>
       </c>
       <c r="P6" s="4">
-        <v>1.135889231281337</v>
+        <v>1.120919439596548</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5521699623279682</v>
+        <v>0.5447706682808832</v>
       </c>
       <c r="R6" s="5">
         <v>782</v>
@@ -3827,22 +3827,22 @@
         <v>120</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5654984684956192</v>
+        <v>0.200446348564185</v>
       </c>
       <c r="O3" s="5">
         <v>1919</v>
       </c>
       <c r="P3" s="4">
-        <v>1.2838818691662</v>
+        <v>1.27547949152538</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5821786606092798</v>
+        <v>0.462672104784934</v>
       </c>
       <c r="R3" s="5">
-        <v>1869</v>
+        <v>1826</v>
       </c>
       <c r="S3" s="5">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3886,16 +3886,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01504386947535139</v>
+        <v>0.03336054567633084</v>
       </c>
       <c r="O4" s="5">
         <v>2392</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4308589635550376</v>
+        <v>0.4326070266248781</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1835396179086448</v>
+        <v>0.1829267735840968</v>
       </c>
       <c r="R4" s="5">
         <v>2390</v>
@@ -3945,22 +3945,22 @@
         <v>12</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3337701042036493</v>
+        <v>0.189222577218402</v>
       </c>
       <c r="O5" s="5">
         <v>1855</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7098370127448501</v>
+        <v>0.6891879544096345</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3534850126525417</v>
+        <v>0.3305243177750612</v>
       </c>
       <c r="R5" s="5">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="S5" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -4004,16 +4004,16 @@
         <v>26</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4174573775069132</v>
+        <v>0.3381587774948684</v>
       </c>
       <c r="O6" s="5">
         <v>911</v>
       </c>
       <c r="P6" s="4">
-        <v>1.037094925595909</v>
+        <v>1.02323226663891</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3805582411866453</v>
+        <v>0.3689104191177843</v>
       </c>
       <c r="R6" s="5">
         <v>890</v>
@@ -4186,22 +4186,22 @@
         <v>44</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5660101474158261</v>
+        <v>0.5094688413458357</v>
       </c>
       <c r="O3" s="5">
         <v>1692</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8494927251575743</v>
+        <v>0.848556820787017</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3889609092000186</v>
+        <v>0.3828796927924308</v>
       </c>
       <c r="R3" s="5">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="S3" s="5">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4245,16 +4245,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.085681912473803</v>
+        <v>0.1339722411834572</v>
       </c>
       <c r="O4" s="5">
         <v>2074</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5611429877440305</v>
+        <v>0.5632970161191341</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2470467522662632</v>
+        <v>0.2429026125804059</v>
       </c>
       <c r="R4" s="5">
         <v>2072</v>
@@ -4304,16 +4304,16 @@
         <v>6</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2796177613218486</v>
+        <v>0.2598620001685106</v>
       </c>
       <c r="O5" s="5">
         <v>1620</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5700554384683532</v>
+        <v>0.5666506295366862</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2773800447849948</v>
+        <v>0.2767975975313011</v>
       </c>
       <c r="R5" s="5">
         <v>1616</v>
@@ -4363,16 +4363,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2747258130716398</v>
+        <v>0.2890148641448889</v>
       </c>
       <c r="O6" s="5">
         <v>646</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9529147951707374</v>
+        <v>0.9548290239854988</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4255189385430211</v>
+        <v>0.4248480960587728</v>
       </c>
       <c r="R6" s="5">
         <v>641</v>
@@ -4545,22 +4545,22 @@
         <v>364</v>
       </c>
       <c r="N3" s="4">
-        <v>1.548832496730614</v>
+        <v>0.2144538034131074</v>
       </c>
       <c r="O3" s="5">
         <v>1655</v>
       </c>
       <c r="P3" s="4">
-        <v>2.606364794722914</v>
+        <v>2.548135046767554</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.357793604604853</v>
+        <v>0.1428684373297302</v>
       </c>
       <c r="R3" s="5">
-        <v>1304</v>
+        <v>1295</v>
       </c>
       <c r="S3" s="5">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4604,16 +4604,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.063568789581591</v>
+        <v>0.08379828816899249</v>
       </c>
       <c r="O4" s="5">
         <v>2494</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3336822220509059</v>
+        <v>0.335663185598873</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1226570495408442</v>
+        <v>0.1213391508064272</v>
       </c>
       <c r="R4" s="5">
         <v>2492</v>
@@ -4663,22 +4663,22 @@
         <v>42</v>
       </c>
       <c r="N5" s="4">
-        <v>0.508411590945261</v>
+        <v>0.3493215162915249</v>
       </c>
       <c r="O5" s="5">
         <v>1854</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7162632061808079</v>
+        <v>0.6814567593324613</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3231448111937371</v>
+        <v>0.2857773194479908</v>
       </c>
       <c r="R5" s="5">
-        <v>1822</v>
+        <v>1816</v>
       </c>
       <c r="S5" s="5">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -4722,16 +4722,16 @@
         <v>54</v>
       </c>
       <c r="N6" s="4">
-        <v>0.6633585853704907</v>
+        <v>0.3399094259057449</v>
       </c>
       <c r="O6" s="5">
         <v>787</v>
       </c>
       <c r="P6" s="4">
-        <v>1.260459535225558</v>
+        <v>1.196820876273943</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3717141252580798</v>
+        <v>0.2170525988731899</v>
       </c>
       <c r="R6" s="5">
         <v>736</v>
